--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
@@ -912,63 +912,66 @@
   </si>
   <si>
     <t>214
-138</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>R$ 604.429,59</t>
-  </si>
-  <si>
-    <t>R$ 4.002,84
-R$ 4.166,03</t>
-  </si>
-  <si>
-    <t>(7.7%)
-(4.2%)</t>
-  </si>
-  <si>
-    <t>44.6</t>
-  </si>
-  <si>
-    <t>(13.6%)</t>
-  </si>
-  <si>
-    <t>53.9%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
+166</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 726.068,14</t>
+  </si>
+  <si>
+    <t>R$ 4.033,71
+R$ 4.186,35</t>
+  </si>
+  <si>
+    <t>(7.4%)
+(3.9%)</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>(13.3%)</t>
+  </si>
+  <si>
+    <t>43.3%</t>
+  </si>
+  <si>
+    <t>(3.5%)</t>
+  </si>
+  <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>26.2</t>
   </si>
   <si>
-    <t>74.7%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
-  </si>
-  <si>
-    <t>4.5</t>
+    <t>74.1%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>4.6</t>
   </si>
   <si>
     <t>6.8</t>
   </si>
   <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>74.3%</t>
-  </si>
-  <si>
-    <t>-R$ 13.705,88</t>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>18.1</t>
+  </si>
+  <si>
+    <t>74.4%</t>
+  </si>
+  <si>
+    <t>-R$ 16.749,01</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>2.3670534883720928</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>5.9403090000000001</v>
+      </c>
       <c r="AD3" s="8">
         <v>12.893797674418606</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.2523800000000005</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>9.4776179999999997</v>
+      </c>
       <c r="AD4" s="8">
         <v>14.721428571428572</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>17.913704444444445</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>22.430368999999999</v>
+      </c>
       <c r="AD5" s="8">
         <v>28.370739999999998</v>
       </c>
@@ -2057,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2093,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>7463.54</v>
+      </c>
+      <c r="P6" s="5">
+        <v>7463.54</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.093402101677868221</v>
+      </c>
+      <c r="R6" s="7">
+        <v>83</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.21698113207547165</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.29385250162791382</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.012914769666940887</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.036519131672101982</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0007827384860267379</v>
+      </c>
+      <c r="X6" s="8">
+        <v>20.880099999999999</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.9392405063291136</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.1146469696969699</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>8.0522080000000003</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.949999999999999</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.9850746268656716</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -2230,7 +2275,9 @@
       <c r="AB7" s="8">
         <v>3.8708343749999998</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>8.8437490000000007</v>
+      </c>
       <c r="AD7" s="8">
         <v>15.773959375</v>
       </c>
@@ -2335,10 +2382,10 @@
         <v>0.098360655737705027</v>
       </c>
       <c r="T8" s="6">
-        <v>0.35406819536570827</v>
+        <v>0.37944138648268166</v>
       </c>
       <c r="U8" s="6">
-        <v>0.0066294849518688092</v>
+        <v>0.03200267606884219</v>
       </c>
       <c r="V8" s="6">
         <v>0.057926532820948597</v>
@@ -2361,7 +2408,9 @@
       <c r="AB8" s="8">
         <v>3.1062023255813953</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>8.2418069999999997</v>
+      </c>
       <c r="AD8" s="8">
         <v>15.124418604651163</v>
       </c>
@@ -2490,7 +2539,9 @@
       <c r="AB9" s="8">
         <v>6.16405294117647</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>12.366339</v>
+      </c>
       <c r="AD9" s="8">
         <v>18.445425490196076</v>
       </c>
@@ -2617,7 +2668,9 @@
       <c r="AB10" s="8">
         <v>3.0333323529411764</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>7.8049010000000001</v>
+      </c>
       <c r="AD10" s="8">
         <v>14.749508823529411</v>
       </c>
@@ -2746,7 +2799,9 @@
       <c r="AB11" s="8">
         <v>5.4939723404255316</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>9.1464529999999993</v>
+      </c>
       <c r="AD11" s="8">
         <v>15.085106382978724</v>
       </c>
@@ -2875,7 +2930,9 @@
       <c r="AB12" s="8">
         <v>7.5434647058823527</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>11.032857</v>
+      </c>
       <c r="AD12" s="8">
         <v>17.182716666666668</v>
       </c>
@@ -2926,7 +2983,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2962,25 +3019,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>5787.3400000000001</v>
+      </c>
+      <c r="P13" s="5">
+        <v>5787.3400000000001</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.24843254081627353</v>
+      </c>
+      <c r="R13" s="7">
+        <v>70</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.15662650602409633</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.32840577882066718</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.025536066655838432</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.035091475531072995</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.031627016902411126</v>
+      </c>
+      <c r="X13" s="8">
+        <v>28.574843396226413</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.62264150943396224</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.15094339622641509</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>6.9811899999999998</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>5.5955981132075481</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>13.102829</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>20.055975471698112</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.660377358490566</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-80.900000000000006</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3099,7 +3192,9 @@
       <c r="AB14" s="8">
         <v>4.9238095238095241</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>9.2007930000000009</v>
+      </c>
       <c r="AD14" s="8">
         <v>16.164285714285715</v>
       </c>
@@ -3150,7 +3245,7 @@
         <v>19519</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C15" s="4">
         <v>44</v>
@@ -3186,25 +3281,61 @@
       <c t="s" r="N15" s="4">
         <v>52</v>
       </c>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="6"/>
+      <c r="O15" s="5">
+        <v>10459.059999999999</v>
+      </c>
+      <c r="P15" s="5">
+        <v>10459.059999999999</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>-0.26277051211744851</v>
+      </c>
+      <c r="R15" s="7">
+        <v>116</v>
+      </c>
+      <c r="S15" s="6">
+        <v>-0.24183006535947715</v>
+      </c>
+      <c r="T15" s="6">
+        <v>0.3283577300445738</v>
+      </c>
+      <c r="U15" s="6">
+        <v>0.0095078525221195791</v>
+      </c>
+      <c r="V15" s="6">
+        <v>0.024959317567735534</v>
+      </c>
+      <c r="W15" s="6">
+        <v>-0.00056305251141115938</v>
+      </c>
+      <c r="X15" s="8">
+        <v>22.485585135135135</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>0.83783783783783783</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>0.027027027027027029</v>
+      </c>
+      <c r="AA15" s="8">
+        <v>4.6126050420168063</v>
+      </c>
+      <c r="AB15" s="8">
+        <v>3.4417808219178081</v>
+      </c>
+      <c r="AC15" s="8">
+        <v>8.7413290000000003</v>
+      </c>
+      <c r="AD15" s="8">
+        <v>15.62680135135135</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>0.8783783783783784</v>
+      </c>
       <c r="AF15" s="9"/>
-      <c r="AG15" s="5"/>
+      <c r="AG15" s="5">
+        <v>0</v>
+      </c>
       <c r="AH15" s="10">
         <v>5</v>
       </c>
@@ -3323,7 +3454,9 @@
       <c r="AB16" s="8">
         <v>19.047438461538462</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>23.579485999999999</v>
+      </c>
       <c r="AD16" s="8">
         <v>30.48076923076923</v>
       </c>
@@ -3452,7 +3585,9 @@
       <c r="AB17" s="8">
         <v>4.0520839285714283</v>
       </c>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="8">
+        <v>7.2259710000000004</v>
+      </c>
       <c r="AD17" s="8">
         <v>14.957758620689654</v>
       </c>
@@ -3581,7 +3716,9 @@
       <c r="AB18" s="8">
         <v>4.9468749999999995</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>8.1663189999999997</v>
+      </c>
       <c r="AD18" s="8">
         <v>15.114583333333334</v>
       </c>
@@ -3710,7 +3847,9 @@
       <c r="AB19" s="8">
         <v>5.0674619047619052</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>10.249999000000001</v>
+      </c>
       <c r="AD19" s="8">
         <v>17.197619047619046</v>
       </c>
@@ -3839,7 +3978,9 @@
       <c r="AB20" s="8">
         <v>4.3740384615384613</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>9.4262809999999995</v>
+      </c>
       <c r="AD20" s="8">
         <v>16.368269230769229</v>
       </c>
@@ -3968,7 +4109,9 @@
       <c r="AB21" s="8">
         <v>5.5557142857142852</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>10.029999</v>
+      </c>
       <c r="AD21" s="8">
         <v>15.980477142857142</v>
       </c>
@@ -4097,7 +4240,9 @@
       <c r="AB22" s="8">
         <v>9.4944444444444454</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>14.735434</v>
+      </c>
       <c r="AD22" s="8">
         <v>21.226575675675676</v>
       </c>
@@ -4226,7 +4371,9 @@
       <c r="AB23" s="8">
         <v>3.9324999999999997</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>8.800224</v>
+      </c>
       <c r="AD23" s="8">
         <v>15.458995238095238</v>
       </c>
@@ -4450,7 +4597,9 @@
       <c r="AB25" s="8">
         <v>3.7912027777777784</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>7.7504619999999997</v>
+      </c>
       <c r="AD25" s="8">
         <v>14.701852777777779</v>
       </c>
@@ -4579,7 +4728,9 @@
       <c r="AB26" s="8">
         <v>10.7291671875</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>16.105881</v>
+      </c>
       <c r="AD26" s="8">
         <v>21.680917391304348</v>
       </c>
@@ -4708,7 +4859,9 @@
       <c r="AB27" s="8">
         <v>8.1068647058823533</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>12.001598</v>
+      </c>
       <c r="AD27" s="8">
         <v>18.703510526315789</v>
       </c>
@@ -4759,7 +4912,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4795,25 +4948,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>5316.2200000000003</v>
+      </c>
+      <c r="P28" s="5">
+        <v>5316.2200000000003</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.24228162826564481</v>
+      </c>
+      <c r="R28" s="7">
+        <v>68</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00042812374205732637</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.3285706761571191</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.075065177889553095</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.066974843027564693</v>
+      </c>
+      <c r="X28" s="8">
+        <v>31.264583333333334</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>6.6037878787878794</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>8.5590291666666669</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>15.70486</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-677.89999999999998</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -4932,7 +5121,9 @@
       <c r="AB29" s="8">
         <v>13.009647368421053</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>23.015789000000002</v>
+      </c>
       <c r="AD29" s="8">
         <v>30.935089473684211</v>
       </c>
@@ -5057,7 +5248,9 @@
       <c r="AB30" s="8">
         <v>11.640000000000001</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>16.18</v>
+      </c>
       <c r="AD30" s="8">
         <v>23.148330000000001</v>
       </c>
@@ -5110,7 +5303,7 @@
         <v>19551</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>44</v>
@@ -5146,25 +5339,61 @@
       <c t="s" r="N31" s="4">
         <v>52</v>
       </c>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="8"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="8"/>
-      <c r="AB31" s="8"/>
-      <c r="AC31" s="8"/>
-      <c r="AD31" s="8"/>
-      <c r="AE31" s="6"/>
+      <c r="O31" s="5">
+        <v>7184.46</v>
+      </c>
+      <c r="P31" s="5">
+        <v>7184.46</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0.14975642855771132</v>
+      </c>
+      <c r="R31" s="7">
+        <v>61</v>
+      </c>
+      <c r="S31" s="6">
+        <v>0.051724137931034475</v>
+      </c>
+      <c r="T31" s="6">
+        <v>0.40803417375836182</v>
+      </c>
+      <c r="U31" s="6">
+        <v>0.055091851022902212</v>
+      </c>
+      <c r="V31" s="6">
+        <v>0.016821514769377238</v>
+      </c>
+      <c r="W31" s="6">
+        <v>0.0059814516331081254</v>
+      </c>
+      <c r="X31" s="8">
+        <v>28.4478641025641</v>
+      </c>
+      <c r="Y31" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z31" s="6">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="AA31" s="8">
+        <v>5.6262295081967215</v>
+      </c>
+      <c r="AB31" s="8">
+        <v>5.7763157894736841</v>
+      </c>
+      <c r="AC31" s="8">
+        <v>12.161785</v>
+      </c>
+      <c r="AD31" s="8">
+        <v>19.850428205128203</v>
+      </c>
+      <c r="AE31" s="6">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="AF31" s="9"/>
-      <c r="AG31" s="5"/>
+      <c r="AG31" s="5">
+        <v>0</v>
+      </c>
       <c r="AH31" s="10">
         <v>5</v>
       </c>
@@ -5283,7 +5512,9 @@
       <c r="AB32" s="8">
         <v>4.526865671641791</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>7.1481880000000002</v>
+      </c>
       <c r="AD32" s="8">
         <v>13.025245588235293</v>
       </c>
@@ -5410,7 +5641,9 @@
       <c r="AB33" s="8">
         <v>4.0462962962962967</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>5.830819</v>
+      </c>
       <c r="AD33" s="8">
         <v>12.757407407407406</v>
       </c>
@@ -5610,10 +5843,10 @@
         <v>0.29166666666666674</v>
       </c>
       <c r="T35" s="6">
-        <v>0.47942586276581411</v>
+        <v>0.84966531706244819</v>
       </c>
       <c r="U35" s="6">
-        <v>0.13453580469265186</v>
+        <v>0.50477525898928588</v>
       </c>
       <c r="V35" s="6">
         <v>0.084947776698409555</v>
@@ -5636,7 +5869,9 @@
       <c r="AB35" s="8">
         <v>3.7956157894736839</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>7.7666659999999998</v>
+      </c>
       <c r="AD35" s="8">
         <v>14.728068421052631</v>
       </c>
@@ -5689,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5725,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>5093.0299999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>5093.0299999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.81092593843670335</v>
+      </c>
+      <c r="R36" s="7">
+        <v>44</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.22222222222222232</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.35338994665258205</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.04371378138357717</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.050794615386125751</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.011758913652580095</v>
+      </c>
+      <c r="X36" s="8">
+        <v>27.818333333333332</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>7.4297619047619055</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>6.1235620689655175</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>20.723889999999997</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>-64.900000000000006</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -5862,7 +6131,9 @@
       <c r="AB37" s="8">
         <v>13.813579629629631</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>19.018340999999999</v>
+      </c>
       <c r="AD37" s="8">
         <v>25.546667272727273</v>
       </c>
@@ -5991,7 +6262,9 @@
       <c r="AB38" s="8">
         <v>3.7653846153846158</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>7.0278840000000002</v>
+      </c>
       <c r="AD38" s="8">
         <v>12.873956250000001</v>
       </c>
@@ -6042,7 +6315,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6078,25 +6351,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>4907.1300000000001</v>
+      </c>
+      <c r="P39" s="5">
+        <v>4907.1300000000001</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.047082245096533137</v>
+      </c>
+      <c r="R39" s="7">
+        <v>59</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.28153888321687015</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.023396995799988995</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.087766780174969888</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.046697968058722714</v>
+      </c>
+      <c r="X39" s="8">
+        <v>19.82136666666667</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.4882189655172415</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>5.9183896551724136</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>8.4072779999999998</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>14.012392307692307</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.97435897435897434</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6215,7 +6524,9 @@
       <c r="AB40" s="8">
         <v>5.1463541666666668</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>8.3423540000000003</v>
+      </c>
       <c r="AD40" s="8">
         <v>15.113775510204082</v>
       </c>
@@ -6344,7 +6655,9 @@
       <c r="AB41" s="8">
         <v>6.4774066666666661</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>10.733789</v>
+      </c>
       <c r="AD41" s="8">
         <v>16.274468085106381</v>
       </c>
@@ -6395,7 +6708,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6431,25 +6744,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>3332.5999999999999</v>
+      </c>
+      <c r="P42" s="5">
+        <v>3332.5999999999999</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.28897707513254611</v>
+      </c>
+      <c r="R42" s="7">
+        <v>42</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.32258064516129037</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.44227056952529559</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.13869378263217907</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.073993128488267418</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0086477525055512223</v>
+      </c>
+      <c r="X42" s="8">
+        <v>25.703333333333333</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>4.5865853658536588</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.7261100000000003</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>10.808332999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>17.765000000000001</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6568,7 +6917,9 @@
       <c r="AB43" s="8">
         <v>8.3543222222222226</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="8">
+        <v>14.264196</v>
+      </c>
       <c r="AD43" s="8">
         <v>21.220988888888886</v>
       </c>
@@ -6697,7 +7048,9 @@
       <c r="AB44" s="8">
         <v>5.2317718749999997</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>8.3954059999999995</v>
+      </c>
       <c r="AD44" s="8">
         <v>16.036363636363639</v>
       </c>
@@ -6826,7 +7179,9 @@
       <c r="AB45" s="8">
         <v>3.2457256410256408</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>7.6379739999999998</v>
+      </c>
       <c r="AD45" s="8">
         <v>13.905982051282052</v>
       </c>
@@ -6877,7 +7232,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -6911,25 +7266,61 @@
       <c t="s" r="N46" s="4">
         <v>52</v>
       </c>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="6"/>
+      <c r="O46" s="5">
+        <v>3419.98</v>
+      </c>
+      <c r="P46" s="5">
+        <v>3419.98</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>0.013723886082853243</v>
+      </c>
+      <c r="R46" s="7">
+        <v>52</v>
+      </c>
+      <c r="S46" s="6">
+        <v>0.26829268292682928</v>
+      </c>
+      <c r="T46" s="6">
+        <v>-23.249900584213943</v>
+      </c>
+      <c r="U46" s="6">
+        <v>-23.639101690653163</v>
+      </c>
+      <c r="V46" s="6">
+        <v>0.05420952754109673</v>
+      </c>
+      <c r="W46" s="6">
+        <v>-0.028910841583868911</v>
+      </c>
+      <c r="X46" s="8">
+        <v>22.716093103448276</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="8">
+        <v>2.2153846153846155</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>6.8398821428571424</v>
+      </c>
+      <c r="AC46" s="8">
+        <v>9.1048220000000004</v>
+      </c>
+      <c r="AD46" s="8">
+        <v>15.614941379310345</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>0.96551724137931039</v>
+      </c>
       <c r="AF46" s="9"/>
-      <c r="AG46" s="5"/>
+      <c r="AG46" s="5">
+        <v>-52.700000000000003</v>
+      </c>
       <c r="AH46" s="10">
         <v>3</v>
       </c>
@@ -7048,7 +7439,9 @@
       <c r="AB47" s="8">
         <v>9.7911453124999994</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>14.169862</v>
+      </c>
       <c r="AD47" s="8">
         <v>20.885384615384616</v>
       </c>
@@ -7158,7 +7551,7 @@
         <v>0.055545265437551644</v>
       </c>
       <c r="W48" s="6">
-        <v>0.015614005861348637</v>
+        <v>0.014171684469179697</v>
       </c>
       <c r="X48" s="8">
         <v>26.273076923076925</v>
@@ -7175,7 +7568,9 @@
       <c r="AB48" s="8">
         <v>3.9096153846153849</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>12.016025000000001</v>
+      </c>
       <c r="AD48" s="8">
         <v>18.951923076923077</v>
       </c>
@@ -7302,7 +7697,9 @@
       <c r="AB49" s="8">
         <v>8.514813888888888</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>12.863887999999999</v>
+      </c>
       <c r="AD49" s="8">
         <v>20.791666666666668</v>
       </c>
@@ -7353,7 +7750,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7389,25 +7786,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>5586.29</v>
+      </c>
+      <c r="P50" s="5">
+        <v>5586.29</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.0067970244571982086</v>
+      </c>
+      <c r="R50" s="7">
+        <v>54</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.18181818181818177</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.9663439599447935</v>
+      </c>
+      <c r="U50" s="6">
+        <v>0.62338825947095478</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.069995023530822778</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.031839109677442454</v>
+      </c>
+      <c r="X50" s="8">
+        <v>22.06011785714286</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.1245098039215686</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>5.0619035714285721</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>7.2464269999999997</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>15.189285714285715</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.9285714285714286</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7621,7 +8054,9 @@
       <c r="AB52" s="8">
         <v>3.7797642857142857</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>7.784662</v>
+      </c>
       <c r="AD52" s="8">
         <v>14.766664705882352</v>
       </c>
@@ -7672,7 +8107,7 @@
         <v>19607</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>44</v>
@@ -7706,25 +8141,61 @@
       <c t="s" r="N53" s="4">
         <v>52</v>
       </c>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="8"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
-      <c r="AA53" s="8"/>
-      <c r="AB53" s="8"/>
-      <c r="AC53" s="8"/>
-      <c r="AD53" s="8"/>
-      <c r="AE53" s="6"/>
+      <c r="O53" s="5">
+        <v>2998.3499999999999</v>
+      </c>
+      <c r="P53" s="5">
+        <v>2998.3499999999999</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>0.0028429519875579068</v>
+      </c>
+      <c r="R53" s="7">
+        <v>40</v>
+      </c>
+      <c r="S53" s="6">
+        <v>0.21212121212121215</v>
+      </c>
+      <c r="T53" s="6">
+        <v>0.49759234245501693</v>
+      </c>
+      <c r="U53" s="6">
+        <v>0.0090002834892524228</v>
+      </c>
+      <c r="V53" s="6">
+        <v>0.049091166808411295</v>
+      </c>
+      <c r="W53" s="6">
+        <v>0.0019952640619007121</v>
+      </c>
+      <c r="X53" s="8">
+        <v>22.472989655172412</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="8">
+        <v>3.2825195121951221</v>
+      </c>
+      <c r="AB53" s="8">
+        <v>3.7172413793103449</v>
+      </c>
+      <c r="AC53" s="8">
+        <v>7.1563210000000002</v>
+      </c>
+      <c r="AD53" s="8">
+        <v>14.074713793103449</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0.93103448275862066</v>
+      </c>
       <c r="AF53" s="9"/>
-      <c r="AG53" s="5"/>
+      <c r="AG53" s="5">
+        <v>-110</v>
+      </c>
       <c r="AH53" s="10">
         <v>3</v>
       </c>
@@ -7843,7 +8314,9 @@
       <c r="AB54" s="8">
         <v>8.6339518518518528</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>12.997045</v>
+      </c>
       <c r="AD54" s="8">
         <v>19.383332142857142</v>
       </c>
@@ -7972,7 +8445,9 @@
       <c r="AB55" s="8">
         <v>28.561262162162159</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>30.901676999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>37.050000000000004</v>
       </c>
@@ -8099,7 +8574,9 @@
       <c r="AB56" s="8">
         <v>2.4083339285714289</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>6.888541</v>
+      </c>
       <c r="AD56" s="8">
         <v>14.6640625</v>
       </c>
@@ -8228,7 +8705,9 @@
       <c r="AB57" s="8">
         <v>4.7856310344827584</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>8.3379300000000001</v>
+      </c>
       <c r="AD57" s="8">
         <v>15.28448275862069</v>
       </c>
@@ -8452,7 +8931,9 @@
       <c r="AB59" s="8">
         <v>7.7398565217391297</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>11.482521</v>
+      </c>
       <c r="AD59" s="8">
         <v>17.175332000000001</v>
       </c>
@@ -8581,7 +9062,9 @@
       <c r="AB60" s="8">
         <v>1.1416500000000001</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>2.9203320000000001</v>
+      </c>
       <c r="AD60" s="8">
         <v>1.9089769230769231</v>
       </c>
@@ -8708,7 +9191,9 @@
       <c r="AB61" s="8">
         <v>3.9880928571428571</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>6.5095229999999997</v>
+      </c>
       <c r="AD61" s="8">
         <v>13.45595</v>
       </c>
@@ -8835,7 +9320,9 @@
       <c r="AB62" s="8">
         <v>3.0362304347826083</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>6.1369249999999997</v>
+      </c>
       <c r="AD62" s="8">
         <v>12.921739130434782</v>
       </c>
@@ -8964,7 +9451,9 @@
       <c r="AB63" s="8">
         <v>9.9106679999999994</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>13.551691</v>
+      </c>
       <c r="AD63" s="8">
         <v>19.395332</v>
       </c>
@@ -9091,7 +9580,9 @@
       <c r="AB64" s="8">
         <v>9.213636363636363</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>13.068844</v>
+      </c>
       <c r="AD64" s="8">
         <v>16.925000000000001</v>
       </c>
@@ -9313,7 +9804,9 @@
       <c r="AB66" s="8">
         <v>13.626923076923077</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>17.401281000000001</v>
+      </c>
       <c r="AD66" s="8">
         <v>24.353846153846156</v>
       </c>
@@ -9440,7 +9933,9 @@
       <c r="AB67" s="8">
         <v>7.2268130434782609</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>9.2027359999999998</v>
+      </c>
       <c r="AD67" s="8">
         <v>14.931411538461539</v>
       </c>
@@ -9569,7 +10064,9 @@
       <c r="AB68" s="8">
         <v>3.6326679999999998</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>7.434666</v>
+      </c>
       <c r="AD68" s="8">
         <v>14.384668</v>
       </c>
@@ -9692,7 +10189,9 @@
       <c r="AB69" s="8">
         <v>9.1434535714285712</v>
       </c>
-      <c r="AC69" s="8"/>
+      <c r="AC69" s="8">
+        <v>12.619007</v>
+      </c>
       <c r="AD69" s="8">
         <v>19.536666666666669</v>
       </c>
@@ -9821,7 +10320,9 @@
       <c r="AB70" s="8">
         <v>7.363490476190476</v>
       </c>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="8">
+        <v>12.157142</v>
+      </c>
       <c r="AD70" s="8">
         <v>19.106347619047618</v>
       </c>
@@ -9948,7 +10449,9 @@
       <c r="AB71" s="8">
         <v>4.2007590909090915</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>7.6056179999999998</v>
+      </c>
       <c r="AD71" s="8">
         <v>15.339856521739131</v>
       </c>
@@ -10075,7 +10578,9 @@
       <c r="AB72" s="8">
         <v>6.1997430769230766</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>10.229486</v>
+      </c>
       <c r="AD72" s="8">
         <v>17.137180000000001</v>
       </c>
@@ -10202,7 +10707,9 @@
       <c r="AB73" s="8">
         <v>12.79895625</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>15.021874</v>
+      </c>
       <c r="AD73" s="8">
         <v>22.96875</v>
       </c>
@@ -10344,7 +10851,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10380,25 +10887,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>3496.6300000000001</v>
+      </c>
+      <c r="P75" s="5">
+        <v>3496.6300000000001</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0.0050444370350783974</v>
+      </c>
+      <c r="R75" s="7">
+        <v>41</v>
+      </c>
+      <c r="S75" s="6">
+        <v>0.10810810810810811</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.3127582844052702</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.057981542227802198</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.024572230976683263</v>
+      </c>
+      <c r="X75" s="8">
+        <v>24.572434615384616</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>4.1317837209302324</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>8.1366680000000002</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>12.367435</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>18.73141153846154</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.76923076923076927</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-76.900000000000006</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10610,7 +11153,9 @@
       <c r="AB77" s="8">
         <v>1.6591650000000002</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>4.1174989999999996</v>
+      </c>
       <c r="AD77" s="8">
         <v>11.055</v>
       </c>
@@ -10659,7 +11204,7 @@
         <v>19666</v>
       </c>
       <c r="B78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C78" s="4">
         <v>44</v>
@@ -10693,25 +11238,61 @@
       <c t="s" r="N78" s="4">
         <v>52</v>
       </c>
-      <c r="O78" s="5"/>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="7"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
-      <c r="V78" s="6"/>
-      <c r="W78" s="6"/>
-      <c r="X78" s="8"/>
-      <c r="Y78" s="6"/>
-      <c r="Z78" s="6"/>
-      <c r="AA78" s="8"/>
-      <c r="AB78" s="8"/>
-      <c r="AC78" s="8"/>
-      <c r="AD78" s="8"/>
-      <c r="AE78" s="6"/>
+      <c r="O78" s="5">
+        <v>5074.3800000000001</v>
+      </c>
+      <c r="P78" s="5">
+        <v>5074.3800000000001</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>-0.073223385019998921</v>
+      </c>
+      <c r="R78" s="7">
+        <v>49</v>
+      </c>
+      <c r="S78" s="6">
+        <v>-0.20967741935483875</v>
+      </c>
+      <c r="T78" s="6">
+        <v>3.2349504372948026</v>
+      </c>
+      <c r="U78" s="6">
+        <v>2.9107965505145459</v>
+      </c>
+      <c r="V78" s="6">
+        <v>0.027596770442891543</v>
+      </c>
+      <c r="W78" s="6">
+        <v>0.0012191637204939322</v>
+      </c>
+      <c r="X78" s="8">
+        <v>23.203251219512197</v>
+      </c>
+      <c r="Y78" s="6">
+        <v>0.80487804878048785</v>
+      </c>
+      <c r="Z78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="8">
+        <v>4.8938775510204087</v>
+      </c>
+      <c r="AB78" s="8">
+        <v>3.5764948717948721</v>
+      </c>
+      <c r="AC78" s="8">
+        <v>8.5313730000000003</v>
+      </c>
+      <c r="AD78" s="8">
+        <v>15.998373170731709</v>
+      </c>
+      <c r="AE78" s="6">
+        <v>0.92682926829268297</v>
+      </c>
       <c r="AF78" s="9"/>
-      <c r="AG78" s="5"/>
+      <c r="AG78" s="5">
+        <v>0</v>
+      </c>
       <c r="AH78" s="10">
         <v>5</v>
       </c>
@@ -10830,7 +11411,9 @@
       <c r="AB79" s="8">
         <v>10.547368421052632</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>17.281534000000001</v>
+      </c>
       <c r="AD79" s="8">
         <v>24.2193</v>
       </c>
@@ -10957,7 +11540,9 @@
       <c r="AB80" s="8">
         <v>9.2403225806451612</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="8">
+        <v>14.215783999999999</v>
+      </c>
       <c r="AD80" s="8">
         <v>22.278702777777781</v>
       </c>
@@ -11084,7 +11669,9 @@
       <c r="AB81" s="8">
         <v>4.9500000000000002</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>12.386362999999999</v>
+      </c>
       <c r="AD81" s="8">
         <v>18.743936363636365</v>
       </c>
@@ -11213,7 +11800,9 @@
       <c r="AB82" s="8">
         <v>7.6500000000000004</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>11.282539</v>
+      </c>
       <c r="AD82" s="8">
         <v>18.177776190476191</v>
       </c>
@@ -11435,7 +12024,9 @@
       <c r="AB84" s="8">
         <v>7.7404785714285707</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>16.404017</v>
+      </c>
       <c r="AD84" s="8">
         <v>22.161456250000001</v>
       </c>
@@ -11564,7 +12155,9 @@
       <c r="AB85" s="8">
         <v>16.972216666666665</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>26.741268999999999</v>
+      </c>
       <c r="AD85" s="8">
         <v>30.809528571428569</v>
       </c>
@@ -11693,7 +12286,9 @@
       <c r="AB86" s="8">
         <v>7.0557281249999999</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>17.045311999999999</v>
+      </c>
       <c r="AD86" s="8">
         <v>25.486978125</v>
       </c>
@@ -11822,7 +12417,9 @@
       <c r="AB87" s="8">
         <v>7.1794846153846148</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>11.43901</v>
+      </c>
       <c r="AD87" s="8">
         <v>13.898414285714285</v>
       </c>
@@ -11949,7 +12546,9 @@
       <c r="AB88" s="8">
         <v>7.3189189189189197</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>9.6873860000000001</v>
+      </c>
       <c r="AD88" s="8">
         <v>15.924324324324326</v>
       </c>
@@ -12200,7 +12799,7 @@
         <v>19698</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C91" s="4">
         <v>44</v>
@@ -12236,11 +12835,21 @@
       <c t="s" r="N91" s="4">
         <v>52</v>
       </c>
-      <c r="O91" s="5"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="7"/>
-      <c r="S91" s="6"/>
+      <c r="O91" s="5">
+        <v>0</v>
+      </c>
+      <c r="P91" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R91" s="7">
+        <v>0</v>
+      </c>
+      <c r="S91" s="6">
+        <v>-1</v>
+      </c>
       <c r="T91" s="6"/>
       <c r="U91" s="6"/>
       <c r="V91" s="6"/>
@@ -12254,7 +12863,9 @@
       <c r="AD91" s="8"/>
       <c r="AE91" s="6"/>
       <c r="AF91" s="9"/>
-      <c r="AG91" s="5"/>
+      <c r="AG91" s="5">
+        <v>0</v>
+      </c>
       <c r="AH91" s="10">
         <v>2</v>
       </c>
@@ -12373,7 +12984,9 @@
       <c r="AB92" s="8">
         <v>3.2405782608695652</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>7.6579699999999997</v>
+      </c>
       <c r="AD92" s="8">
         <v>15.559421739130434</v>
       </c>
@@ -12474,10 +13087,10 @@
         <v>0.87755102040816335</v>
       </c>
       <c r="T93" s="6">
-        <v>0.3315654681229202</v>
+        <v>0.31570867107199174</v>
       </c>
       <c r="U93" s="6">
-        <v>0.021831211534709072</v>
+        <v>0.0059744144837806335</v>
       </c>
       <c r="V93" s="6">
         <v>0.043950500740959499</v>
@@ -12500,7 +13113,9 @@
       <c r="AB93" s="8">
         <v>2.6253333333333333</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>4.9177770000000001</v>
+      </c>
       <c r="AD93" s="8">
         <v>11.864666666666666</v>
       </c>
@@ -12551,7 +13166,7 @@
         <v>19706</v>
       </c>
       <c r="B94" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C94" s="4">
         <v>44</v>
@@ -12585,25 +13200,61 @@
       <c t="s" r="N94" s="4">
         <v>52</v>
       </c>
-      <c r="O94" s="5"/>
-      <c r="P94" s="5"/>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="7"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
-      <c r="V94" s="6"/>
-      <c r="W94" s="6"/>
-      <c r="X94" s="8"/>
-      <c r="Y94" s="6"/>
-      <c r="Z94" s="6"/>
-      <c r="AA94" s="8"/>
-      <c r="AB94" s="8"/>
-      <c r="AC94" s="8"/>
-      <c r="AD94" s="8"/>
-      <c r="AE94" s="6"/>
+      <c r="O94" s="5">
+        <v>2322.8000000000002</v>
+      </c>
+      <c r="P94" s="5">
+        <v>2322.8000000000002</v>
+      </c>
+      <c r="Q94" s="6">
+        <v>-0.14596033502709782</v>
+      </c>
+      <c r="R94" s="7">
+        <v>27</v>
+      </c>
+      <c r="S94" s="6">
+        <v>-0.22857142857142854</v>
+      </c>
+      <c r="T94" s="6">
+        <v>0.0041286378508696396</v>
+      </c>
+      <c r="U94" s="6">
+        <v>-0.38193990012054413</v>
+      </c>
+      <c r="V94" s="6">
+        <v>0.30755101601515411</v>
+      </c>
+      <c r="W94" s="6">
+        <v>0.25409828655071465</v>
+      </c>
+      <c r="X94" s="8">
+        <v>41.354168749999999</v>
+      </c>
+      <c r="Y94" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="Z94" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA94" s="8">
+        <v>9.8311099999999989</v>
+      </c>
+      <c r="AB94" s="8">
+        <v>10.413543750000001</v>
+      </c>
+      <c r="AC94" s="8">
+        <v>21.970206999999998</v>
+      </c>
+      <c r="AD94" s="8">
+        <v>28.653124999999999</v>
+      </c>
+      <c r="AE94" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF94" s="9"/>
-      <c r="AG94" s="5"/>
+      <c r="AG94" s="5">
+        <v>0</v>
+      </c>
       <c r="AH94" s="10">
         <v>3</v>
       </c>
@@ -12815,7 +13466,9 @@
       <c r="AB96" s="8">
         <v>2.3012820512820511</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>4.2116980000000002</v>
+      </c>
       <c r="AD96" s="8">
         <v>11.17521282051282</v>
       </c>
@@ -12944,7 +13597,9 @@
       <c r="AB97" s="8">
         <v>3.8245631578947372</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>10.571529999999999</v>
+      </c>
       <c r="AD97" s="8">
         <v>15.684850000000001</v>
       </c>
@@ -13073,7 +13728,9 @@
       <c r="AB98" s="8">
         <v>7.979166666666667</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>15.82361</v>
+      </c>
       <c r="AD98" s="8">
         <v>22.755558333333337</v>
       </c>
@@ -13202,7 +13859,9 @@
       <c r="AB99" s="8">
         <v>7.6102557692307693</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>12.185104000000001</v>
+      </c>
       <c r="AD99" s="8">
         <v>18.600616666666667</v>
       </c>
@@ -13331,7 +13990,9 @@
       <c r="AB100" s="8">
         <v>15.706945833333334</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="8">
+        <v>24.877776999999998</v>
+      </c>
       <c r="AD100" s="8">
         <v>33.835416666666667</v>
       </c>
@@ -13458,7 +14119,9 @@
       <c r="AB101" s="8">
         <v>8.0574055555555546</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>9.3328450000000007</v>
+      </c>
       <c r="AD101" s="8">
         <v>15.511405263157895</v>
       </c>
@@ -13682,7 +14345,9 @@
       <c r="AB103" s="8">
         <v>28.242307692307691</v>
       </c>
-      <c r="AC103" s="8"/>
+      <c r="AC103" s="8">
+        <v>38.232430000000001</v>
+      </c>
       <c r="AD103" s="8">
         <v>42.89506296296296</v>
       </c>
@@ -13811,7 +14476,9 @@
       <c r="AB104" s="8">
         <v>6.7739130434782613</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>12.249838</v>
+      </c>
       <c r="AD104" s="8">
         <v>19.52</v>
       </c>
@@ -13934,7 +14601,9 @@
       <c r="AB105" s="8">
         <v>12.574446666666667</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>15.128147</v>
+      </c>
       <c r="AD105" s="8">
         <v>19.320588235294117</v>
       </c>
@@ -14063,7 +14732,9 @@
       <c r="AB106" s="8">
         <v>2.3647058823529412</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>7.3343119999999997</v>
+      </c>
       <c r="AD106" s="8">
         <v>14.287252941176471</v>
       </c>
@@ -14192,7 +14863,9 @@
       <c r="AB107" s="8">
         <v>5.8858350000000002</v>
       </c>
-      <c r="AC107" s="8"/>
+      <c r="AC107" s="8">
+        <v>10.859166</v>
+      </c>
       <c r="AD107" s="8">
         <v>17.811664999999998</v>
       </c>
@@ -14412,7 +15085,9 @@
       <c r="AB109" s="8">
         <v>11.789999999999999</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>17.909790999999998</v>
+      </c>
       <c r="AD109" s="8">
         <v>25.79222</v>
       </c>
@@ -14634,7 +15309,9 @@
       <c r="AB111" s="8">
         <v>2.5291625</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>8.3069430000000004</v>
+      </c>
       <c r="AD111" s="8">
         <v>15.1645875</v>
       </c>
@@ -14854,7 +15531,9 @@
       <c r="AB113" s="8">
         <v>2.6725000000000003</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>4.21</v>
+      </c>
       <c r="AD113" s="8">
         <v>14.155000000000001</v>
       </c>
@@ -14983,7 +15662,9 @@
       <c r="AB114" s="8">
         <v>4.0728052631578953</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="8">
+        <v>6.1069329999999997</v>
+      </c>
       <c r="AD114" s="8">
         <v>14.228947368421053</v>
       </c>
@@ -15112,7 +15793,9 @@
       <c r="AB115" s="8">
         <v>3.9077800000000003</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>6.1744430000000001</v>
+      </c>
       <c r="AD115" s="8">
         <v>13.626043749999999</v>
       </c>
@@ -15334,7 +16017,9 @@
       <c r="AB117" s="8">
         <v>3.8706333333333331</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>8.1563479999999995</v>
+      </c>
       <c r="AD117" s="8">
         <v>11.885714285714286</v>
       </c>
@@ -15463,7 +16148,9 @@
       <c r="AB118" s="8">
         <v>9.7555555555555546</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>15.466666</v>
+      </c>
       <c r="AD118" s="8">
         <v>22.420372222222223</v>
       </c>
@@ -15592,7 +16279,9 @@
       <c r="AB119" s="8">
         <v>3.9009823529411762</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>6.4450969999999996</v>
+      </c>
       <c r="AD119" s="8">
         <v>13.393135294117647</v>
       </c>
@@ -15719,7 +16408,9 @@
       <c r="AB120" s="8">
         <v>9.4895812500000005</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>13.209374</v>
+      </c>
       <c r="AD120" s="8">
         <v>21.175000000000001</v>
       </c>
@@ -15846,7 +16537,9 @@
       <c r="AB121" s="8">
         <v>12.496666666666666</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>18.015554000000002</v>
+      </c>
       <c r="AD121" s="8">
         <v>25.897780000000001</v>
       </c>
@@ -15975,7 +16668,9 @@
       <c r="AB122" s="8">
         <v>6.564446666666667</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>10.80111</v>
+      </c>
       <c r="AD122" s="8">
         <v>17.261113333333334</v>
       </c>
@@ -16104,7 +16799,9 @@
       <c r="AB123" s="8">
         <v>6.8399000000000001</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>8.8153600000000001</v>
+      </c>
       <c r="AD123" s="8">
         <v>15.975463888888889</v>
       </c>
@@ -16229,7 +16926,9 @@
       <c r="AB124" s="8">
         <v>6.9984818181818182</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>11.441539000000001</v>
+      </c>
       <c r="AD124" s="8">
         <v>19.513636363636365</v>
       </c>
@@ -16358,7 +17057,9 @@
       <c r="AB125" s="8">
         <v>7.2336607843137255</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>13.280454000000001</v>
+      </c>
       <c r="AD125" s="8">
         <v>21.049999999999997</v>
       </c>
@@ -16487,7 +17188,9 @@
       <c r="AB126" s="8">
         <v>17.710782352941177</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>23.106397999999999</v>
+      </c>
       <c r="AD126" s="8">
         <v>30.099017647058822</v>
       </c>
@@ -16616,7 +17319,9 @@
       <c r="AB127" s="8">
         <v>8.8333363636363647</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>14.834847999999999</v>
+      </c>
       <c r="AD127" s="8">
         <v>24.68939090909091</v>
       </c>
@@ -16745,7 +17450,9 @@
       <c r="AB128" s="8">
         <v>15.273814285714286</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>26.859224999999999</v>
+      </c>
       <c r="AD128" s="8">
         <v>33.423814285714286</v>
       </c>
@@ -16874,7 +17581,9 @@
       <c r="AB129" s="8">
         <v>8.091271428571428</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>14.314753</v>
+      </c>
       <c r="AD129" s="8">
         <v>20.642422727272727</v>
       </c>
@@ -17003,7 +17712,9 @@
       <c r="AB130" s="8">
         <v>13.651192857142858</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>17.88119</v>
+      </c>
       <c r="AD130" s="8">
         <v>23.746666666666666</v>
       </c>
@@ -17130,7 +17841,9 @@
       <c r="AB131" s="8">
         <v>15.343592307692308</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>22.317947</v>
+      </c>
       <c r="AD131" s="8">
         <v>29.270515384615386</v>
       </c>
@@ -17181,7 +17894,7 @@
         <v>19774</v>
       </c>
       <c r="B132" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C132" s="4">
         <v>44</v>
@@ -17217,25 +17930,61 @@
       <c t="s" r="N132" s="4">
         <v>52</v>
       </c>
-      <c r="O132" s="5"/>
-      <c r="P132" s="5"/>
-      <c r="Q132" s="6"/>
-      <c r="R132" s="7"/>
-      <c r="S132" s="6"/>
-      <c r="T132" s="6"/>
-      <c r="U132" s="6"/>
-      <c r="V132" s="6"/>
-      <c r="W132" s="6"/>
-      <c r="X132" s="8"/>
-      <c r="Y132" s="6"/>
-      <c r="Z132" s="6"/>
-      <c r="AA132" s="8"/>
-      <c r="AB132" s="8"/>
-      <c r="AC132" s="8"/>
-      <c r="AD132" s="8"/>
-      <c r="AE132" s="6"/>
+      <c r="O132" s="5">
+        <v>6581.3199999999997</v>
+      </c>
+      <c r="P132" s="5">
+        <v>6581.3199999999997</v>
+      </c>
+      <c r="Q132" s="6">
+        <v>-0.25202243028042393</v>
+      </c>
+      <c r="R132" s="7">
+        <v>83</v>
+      </c>
+      <c r="S132" s="6">
+        <v>-0.27826086956521734</v>
+      </c>
+      <c r="T132" s="6">
+        <v>0.28328400685576755</v>
+      </c>
+      <c r="U132" s="6">
+        <v>-0.006673023040970504</v>
+      </c>
+      <c r="V132" s="6">
+        <v>0.024008405608601315</v>
+      </c>
+      <c r="W132" s="6">
+        <v>-0.027969009256501736</v>
+      </c>
+      <c r="X132" s="8">
+        <v>23.772435897435898</v>
+      </c>
+      <c r="Y132" s="6">
+        <v>0.41025641025641024</v>
+      </c>
+      <c r="Z132" s="6">
+        <v>0.089743589743589744</v>
+      </c>
+      <c r="AA132" s="8">
+        <v>3.7845524390243903</v>
+      </c>
+      <c r="AB132" s="8">
+        <v>7.3928893333333328</v>
+      </c>
+      <c r="AC132" s="8">
+        <v>11.181990000000001</v>
+      </c>
+      <c r="AD132" s="8">
+        <v>16.717948717948719</v>
+      </c>
+      <c r="AE132" s="6">
+        <v>0.71794871794871795</v>
+      </c>
       <c r="AF132" s="9"/>
-      <c r="AG132" s="5"/>
+      <c r="AG132" s="5">
+        <v>0</v>
+      </c>
       <c r="AH132" s="10">
         <v>4</v>
       </c>
@@ -17354,7 +18103,9 @@
       <c r="AB133" s="8">
         <v>6.4166636363636362</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="8">
+        <v>13.27361</v>
+      </c>
       <c r="AD133" s="8">
         <v>19.205558333333332</v>
       </c>
@@ -17483,7 +18234,9 @@
       <c r="AB134" s="8">
         <v>16.307411111111108</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>20.822220999999999</v>
+      </c>
       <c r="AD134" s="8">
         <v>28.042588888888886</v>
       </c>
@@ -17612,7 +18365,9 @@
       <c r="AB135" s="8">
         <v>2.6675</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>5.5125000000000002</v>
+      </c>
       <c r="AD135" s="8">
         <v>12.478335</v>
       </c>
@@ -17741,7 +18496,9 @@
       <c r="AB136" s="8">
         <v>2.1149999999999998</v>
       </c>
-      <c r="AC136" s="8"/>
+      <c r="AC136" s="8">
+        <v>6.3831810000000004</v>
+      </c>
       <c r="AD136" s="8">
         <v>12.663636363636364</v>
       </c>
@@ -17868,7 +18625,9 @@
       <c r="AB137" s="8">
         <v>3.9380999999999999</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>9.1952370000000005</v>
+      </c>
       <c r="AD137" s="8">
         <v>16.12142857142857</v>
       </c>
@@ -17995,7 +18754,9 @@
       <c r="AB138" s="8">
         <v>6.8930379746835433</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>11.422783000000001</v>
+      </c>
       <c r="AD138" s="8">
         <v>17.471285542168676</v>
       </c>
@@ -18046,7 +18807,7 @@
         <v>19790</v>
       </c>
       <c r="B139" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C139" s="4">
         <v>44</v>
@@ -18082,25 +18843,61 @@
       <c t="s" r="N139" s="4">
         <v>52</v>
       </c>
-      <c r="O139" s="5"/>
-      <c r="P139" s="5"/>
-      <c r="Q139" s="6"/>
-      <c r="R139" s="7"/>
-      <c r="S139" s="6"/>
-      <c r="T139" s="6"/>
-      <c r="U139" s="6"/>
-      <c r="V139" s="6"/>
-      <c r="W139" s="6"/>
-      <c r="X139" s="8"/>
-      <c r="Y139" s="6"/>
-      <c r="Z139" s="6"/>
-      <c r="AA139" s="8"/>
-      <c r="AB139" s="8"/>
-      <c r="AC139" s="8"/>
-      <c r="AD139" s="8"/>
-      <c r="AE139" s="6"/>
+      <c r="O139" s="5">
+        <v>5116.8299999999999</v>
+      </c>
+      <c r="P139" s="5">
+        <v>5116.8299999999999</v>
+      </c>
+      <c r="Q139" s="6">
+        <v>0.52837915337467289</v>
+      </c>
+      <c r="R139" s="7">
+        <v>45</v>
+      </c>
+      <c r="S139" s="6">
+        <v>0.18421052631578938</v>
+      </c>
+      <c r="T139" s="6">
+        <v>0.0020762855127100179</v>
+      </c>
+      <c r="U139" s="6">
+        <v>-0.28683110441425647</v>
+      </c>
+      <c r="V139" s="6">
+        <v>0.019365798746489526</v>
+      </c>
+      <c r="W139" s="6">
+        <v>-0.0030093827623743608</v>
+      </c>
+      <c r="X139" s="8">
+        <v>24.5625</v>
+      </c>
+      <c r="Y139" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="8">
+        <v>2.3075404761904763</v>
+      </c>
+      <c r="AB139" s="8">
+        <v>5.1515181818181821</v>
+      </c>
+      <c r="AC139" s="8">
+        <v>7.9584590000000004</v>
+      </c>
+      <c r="AD139" s="8">
+        <v>13.922224999999999</v>
+      </c>
+      <c r="AE139" s="6">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="AF139" s="9"/>
-      <c r="AG139" s="5"/>
+      <c r="AG139" s="5">
+        <v>0</v>
+      </c>
       <c r="AH139" s="10">
         <v>5</v>
       </c>
@@ -18407,7 +19204,9 @@
       <c r="AB142" s="8">
         <v>4.5460000000000003</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>8.1233799999999992</v>
+      </c>
       <c r="AD142" s="8">
         <v>16.313096428571431</v>
       </c>
@@ -18534,7 +19333,9 @@
       <c r="AB143" s="8">
         <v>4.8122558823529413</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>9.1955869999999997</v>
+      </c>
       <c r="AD143" s="8">
         <v>16.714352777777776</v>
       </c>
@@ -18585,7 +19386,7 @@
         <v>19798</v>
       </c>
       <c r="B144" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C144" s="4">
         <v>44</v>
@@ -18621,25 +19422,61 @@
       <c t="s" r="N144" s="4">
         <v>52</v>
       </c>
-      <c r="O144" s="5"/>
-      <c r="P144" s="5"/>
-      <c r="Q144" s="6"/>
-      <c r="R144" s="7"/>
-      <c r="S144" s="6"/>
-      <c r="T144" s="6"/>
-      <c r="U144" s="6"/>
-      <c r="V144" s="6"/>
-      <c r="W144" s="6"/>
-      <c r="X144" s="8"/>
-      <c r="Y144" s="6"/>
-      <c r="Z144" s="6"/>
-      <c r="AA144" s="8"/>
-      <c r="AB144" s="8"/>
-      <c r="AC144" s="8"/>
-      <c r="AD144" s="8"/>
-      <c r="AE144" s="6"/>
+      <c r="O144" s="5">
+        <v>6460.2799999999997</v>
+      </c>
+      <c r="P144" s="5">
+        <v>6460.2799999999997</v>
+      </c>
+      <c r="Q144" s="6">
+        <v>0.68181711682395041</v>
+      </c>
+      <c r="R144" s="7">
+        <v>84</v>
+      </c>
+      <c r="S144" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="T144" s="6">
+        <v>-0.1017386243320723</v>
+      </c>
+      <c r="U144" s="6">
+        <v>-0.41995702972626575</v>
+      </c>
+      <c r="V144" s="6">
+        <v>0.020535410229897157</v>
+      </c>
+      <c r="W144" s="6">
+        <v>-0.0080856402508869586</v>
+      </c>
+      <c r="X144" s="8">
+        <v>23.671726785714288</v>
+      </c>
+      <c r="Y144" s="6">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="Z144" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="8">
+        <v>2.8421686746987951</v>
+      </c>
+      <c r="AB144" s="8">
+        <v>5.1880509433962265</v>
+      </c>
+      <c r="AC144" s="8">
+        <v>7.8678739999999996</v>
+      </c>
+      <c r="AD144" s="8">
+        <v>14.220535714285715</v>
+      </c>
+      <c r="AE144" s="6">
+        <v>0.7857142857142857</v>
+      </c>
       <c r="AF144" s="9"/>
-      <c r="AG144" s="5"/>
+      <c r="AG144" s="5">
+        <v>-327.32999999999998</v>
+      </c>
       <c r="AH144" s="10">
         <v>5</v>
       </c>
@@ -18758,7 +19595,9 @@
       <c r="AB145" s="8">
         <v>4.9333375000000004</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>9.9558330000000002</v>
+      </c>
       <c r="AD145" s="8">
         <v>10.980835000000001</v>
       </c>
@@ -18887,7 +19726,9 @@
       <c r="AB146" s="8">
         <v>3.1902749999999997</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>6.4140860000000002</v>
+      </c>
       <c r="AD146" s="8">
         <v>11.688092857142857</v>
       </c>
@@ -19016,7 +19857,9 @@
       <c r="AB147" s="8">
         <v>2.2013319999999998</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>5.6913330000000002</v>
+      </c>
       <c r="AD147" s="8">
         <v>12.65</v>
       </c>
@@ -19147,7 +19990,9 @@
       <c r="AB148" s="8">
         <v>10.006578947368421</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>16.473244000000001</v>
+      </c>
       <c r="AD148" s="8">
         <v>23.926923076923078</v>
       </c>
@@ -19198,7 +20043,7 @@
         <v>19817</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>44</v>
@@ -19234,25 +20079,61 @@
       <c t="s" r="N149" s="4">
         <v>52</v>
       </c>
-      <c r="O149" s="5"/>
-      <c r="P149" s="5"/>
-      <c r="Q149" s="6"/>
-      <c r="R149" s="7"/>
-      <c r="S149" s="6"/>
-      <c r="T149" s="6"/>
-      <c r="U149" s="6"/>
-      <c r="V149" s="6"/>
-      <c r="W149" s="6"/>
-      <c r="X149" s="8"/>
-      <c r="Y149" s="6"/>
-      <c r="Z149" s="6"/>
-      <c r="AA149" s="8"/>
-      <c r="AB149" s="8"/>
-      <c r="AC149" s="8"/>
-      <c r="AD149" s="8"/>
-      <c r="AE149" s="6"/>
+      <c r="O149" s="5">
+        <v>3369.5700000000002</v>
+      </c>
+      <c r="P149" s="5">
+        <v>3369.5700000000002</v>
+      </c>
+      <c r="Q149" s="6">
+        <v>-0.019821334551198277</v>
+      </c>
+      <c r="R149" s="7">
+        <v>38</v>
+      </c>
+      <c r="S149" s="6">
+        <v>0</v>
+      </c>
+      <c r="T149" s="6">
+        <v>0.37911861157358356</v>
+      </c>
+      <c r="U149" s="6">
+        <v>0.0074866229222126266</v>
+      </c>
+      <c r="V149" s="6">
+        <v>0.033423552560118946</v>
+      </c>
+      <c r="W149" s="6">
+        <v>-0.038428345456541932</v>
+      </c>
+      <c r="X149" s="8">
+        <v>48.36904642857143</v>
+      </c>
+      <c r="Y149" s="6">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Z149" s="6">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="AA149" s="8">
+        <v>8.3548236842105261</v>
+      </c>
+      <c r="AB149" s="8">
+        <v>28.70448846153846</v>
+      </c>
+      <c r="AC149" s="8">
+        <v>37.965041999999997</v>
+      </c>
+      <c r="AD149" s="8">
+        <v>42.507739285714287</v>
+      </c>
+      <c r="AE149" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF149" s="9"/>
-      <c r="AG149" s="5"/>
+      <c r="AG149" s="5">
+        <v>0</v>
+      </c>
       <c r="AH149" s="10">
         <v>2</v>
       </c>
@@ -19369,7 +20250,9 @@
       <c r="AB150" s="8">
         <v>2.706142105263158</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>5.8311400000000004</v>
+      </c>
       <c r="AD150" s="8">
         <v>12.559165</v>
       </c>
@@ -19597,7 +20480,9 @@
       <c r="AB152" s="8">
         <v>3.9549999999999996</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>6.2949999999999999</v>
+      </c>
       <c r="AD152" s="8">
         <v>13.21833</v>
       </c>
@@ -19726,7 +20611,9 @@
       <c r="AB153" s="8">
         <v>9.5426288461538462</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>13.857371000000001</v>
+      </c>
       <c r="AD153" s="8">
         <v>21.783332692307695</v>
       </c>
@@ -19855,7 +20742,9 @@
       <c r="AB154" s="8">
         <v>6.3705153846153841</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>9.4062260000000002</v>
+      </c>
       <c r="AD154" s="8">
         <v>18.488461538461539</v>
       </c>
@@ -19982,7 +20871,9 @@
       <c r="AB155" s="8">
         <v>2.7774783783783783</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>5.8301790000000002</v>
+      </c>
       <c r="AD155" s="8">
         <v>11.888737837837839</v>
       </c>
@@ -20111,7 +21002,9 @@
       <c r="AB156" s="8">
         <v>3.5935923076923078</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>7.5947789999999999</v>
+      </c>
       <c r="AD156" s="8">
         <v>13.873807142857144</v>
       </c>
@@ -20402,7 +21295,9 @@
       <c r="Z159" s="6"/>
       <c r="AA159" s="8"/>
       <c r="AB159" s="8"/>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>8.5398800000000001</v>
+      </c>
       <c r="AD159" s="8"/>
       <c r="AE159" s="6"/>
       <c r="AF159" s="9"/>
@@ -20445,7 +21340,7 @@
         <v>19866</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>44</v>
@@ -20479,25 +21374,61 @@
       <c t="s" r="N160" s="4">
         <v>52</v>
       </c>
-      <c r="O160" s="5"/>
-      <c r="P160" s="5"/>
-      <c r="Q160" s="6"/>
-      <c r="R160" s="7"/>
-      <c r="S160" s="6"/>
-      <c r="T160" s="6"/>
-      <c r="U160" s="6"/>
-      <c r="V160" s="6"/>
-      <c r="W160" s="6"/>
-      <c r="X160" s="8"/>
-      <c r="Y160" s="6"/>
-      <c r="Z160" s="6"/>
-      <c r="AA160" s="8"/>
-      <c r="AB160" s="8"/>
-      <c r="AC160" s="8"/>
-      <c r="AD160" s="8"/>
-      <c r="AE160" s="6"/>
+      <c r="O160" s="5">
+        <v>2649.73</v>
+      </c>
+      <c r="P160" s="5">
+        <v>2649.73</v>
+      </c>
+      <c r="Q160" s="6">
+        <v>-0.42598578032728651</v>
+      </c>
+      <c r="R160" s="7">
+        <v>29</v>
+      </c>
+      <c r="S160" s="6">
+        <v>-0.40816326530612246</v>
+      </c>
+      <c r="T160" s="6">
+        <v>0.30952972567016263</v>
+      </c>
+      <c r="U160" s="6">
+        <v>0.0065101727345805039</v>
+      </c>
+      <c r="V160" s="6">
+        <v>0.033044687571941289</v>
+      </c>
+      <c r="W160" s="6">
+        <v>-0.020821178006815787</v>
+      </c>
+      <c r="X160" s="8">
+        <v>30.594926086956523</v>
+      </c>
+      <c r="Y160" s="6">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="Z160" s="6">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="AA160" s="8">
+        <v>5.1063206896551723</v>
+      </c>
+      <c r="AB160" s="8">
+        <v>7.4760869565217387</v>
+      </c>
+      <c r="AC160" s="8">
+        <v>12.799999</v>
+      </c>
+      <c r="AD160" s="8">
+        <v>19.755073913043478</v>
+      </c>
+      <c r="AE160" s="6">
+        <v>0.47826086956521741</v>
+      </c>
       <c r="AF160" s="9"/>
-      <c r="AG160" s="5"/>
+      <c r="AG160" s="5">
+        <v>0</v>
+      </c>
       <c r="AH160" s="10">
         <v>2</v>
       </c>
@@ -20536,7 +21467,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>44</v>
@@ -20572,25 +21503,57 @@
       <c t="s" r="N161" s="4">
         <v>52</v>
       </c>
-      <c r="O161" s="5"/>
-      <c r="P161" s="5"/>
-      <c r="Q161" s="6"/>
-      <c r="R161" s="7"/>
-      <c r="S161" s="6"/>
-      <c r="T161" s="6"/>
-      <c r="U161" s="6"/>
-      <c r="V161" s="6"/>
-      <c r="W161" s="6"/>
-      <c r="X161" s="8"/>
-      <c r="Y161" s="6"/>
-      <c r="Z161" s="6"/>
-      <c r="AA161" s="8"/>
+      <c r="O161" s="5">
+        <v>3205.9000000000001</v>
+      </c>
+      <c r="P161" s="5">
+        <v>3205.9000000000001</v>
+      </c>
+      <c r="Q161" s="6">
+        <v>0.25485852066118952</v>
+      </c>
+      <c r="R161" s="7">
+        <v>41</v>
+      </c>
+      <c r="S161" s="6">
+        <v>0.024999999999999911</v>
+      </c>
+      <c r="T161" s="6">
+        <v>0.5781668174303628</v>
+      </c>
+      <c r="U161" s="6">
+        <v>0.37179731120746123</v>
+      </c>
+      <c r="V161" s="6">
+        <v>0.01508468760722418</v>
+      </c>
+      <c r="W161" s="6">
+        <v>-0.033048441935182006</v>
+      </c>
+      <c r="X161" s="8">
+        <v>2.9333</v>
+      </c>
+      <c r="Y161" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="8">
+        <v>10.553507894736843</v>
+      </c>
       <c r="AB161" s="8"/>
       <c r="AC161" s="8"/>
-      <c r="AD161" s="8"/>
-      <c r="AE161" s="6"/>
+      <c r="AD161" s="8">
+        <v>1.9666999999999999</v>
+      </c>
+      <c r="AE161" s="6">
+        <v>1</v>
+      </c>
       <c r="AF161" s="9"/>
-      <c r="AG161" s="5"/>
+      <c r="AG161" s="5">
+        <v>-1025.8</v>
+      </c>
       <c r="AH161" s="10">
         <v>5</v>
       </c>
@@ -20631,7 +21594,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20667,25 +21630,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>2874.8000000000002</v>
+      </c>
+      <c r="P162" s="5">
+        <v>2874.8000000000002</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.34277667026354763</v>
+      </c>
+      <c r="R162" s="7">
+        <v>31</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.4464285714285714</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.18262473911228605</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.14498761652984554</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.072545046611938224</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.048992103798525109</v>
+      </c>
+      <c r="X162" s="8">
+        <v>20.402561538461537</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>3.1066666666666669</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>1.6205153846153846</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>5.4038449999999996</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>13.330769230769231</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.92307692307692313</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>0</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20804,7 +21803,9 @@
       <c r="AB163" s="8">
         <v>12.189138202247191</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>17.902435000000001</v>
+      </c>
       <c r="AD163" s="8">
         <v>24.989893617021277</v>
       </c>
@@ -20933,7 +21934,9 @@
       <c r="AB164" s="8">
         <v>4.0819458333333332</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>9.0881340000000002</v>
+      </c>
       <c r="AD164" s="8">
         <v>13.587620000000001</v>
       </c>
@@ -21157,7 +22160,9 @@
       <c r="AB166" s="8">
         <v>8.5362764705882359</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>12.820587</v>
+      </c>
       <c r="AD166" s="8">
         <v>19.741176470588236</v>
       </c>
@@ -21286,7 +22291,9 @@
       <c r="AB167" s="8">
         <v>6.5614285714285714</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>9.0144979999999997</v>
+      </c>
       <c r="AD167" s="8">
         <v>14.82882972972973</v>
       </c>
@@ -21415,7 +22422,9 @@
       <c r="AB168" s="8">
         <v>4.2147058823529413</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>7.9774500000000002</v>
+      </c>
       <c r="AD168" s="8">
         <v>14.807841176470589</v>
       </c>
@@ -21544,7 +22553,9 @@
       <c r="AB169" s="8">
         <v>4.9214285714285708</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>11.441882</v>
+      </c>
       <c r="AD169" s="8">
         <v>18.073486363636363</v>
       </c>
@@ -21673,7 +22684,9 @@
       <c r="AB170" s="8">
         <v>3.0175421052631579</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>7.7267089999999996</v>
+      </c>
       <c r="AD170" s="8">
         <v>14.708773684210527</v>
       </c>
@@ -21802,7 +22815,9 @@
       <c r="AB171" s="8">
         <v>4.7446954545454547</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>9.2190539999999999</v>
+      </c>
       <c r="AD171" s="8">
         <v>14.830769230769231</v>
       </c>
@@ -21931,7 +22946,9 @@
       <c r="AB172" s="8">
         <v>5.4314833333333334</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>8.2787030000000001</v>
+      </c>
       <c r="AD172" s="8">
         <v>15.24073888888889</v>
       </c>
@@ -22060,7 +23077,9 @@
       <c r="AB173" s="8">
         <v>7.5615384615384613</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>16.155704</v>
+      </c>
       <c r="AD173" s="8">
         <v>18.569165000000002</v>
       </c>
@@ -22189,7 +23208,9 @@
       <c r="AB174" s="8">
         <v>2.5100868421052631</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>9.3478060000000003</v>
+      </c>
       <c r="AD174" s="8">
         <v>16.310526315789474</v>
       </c>
@@ -22240,7 +23261,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22276,25 +23297,61 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
-      <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="O175" s="5">
+        <v>2841.04</v>
+      </c>
+      <c r="P175" s="5">
+        <v>2841.04</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>0.0060660573460202816</v>
+      </c>
+      <c r="R175" s="7">
+        <v>40</v>
+      </c>
+      <c r="S175" s="6">
+        <v>-0.090909090909090939</v>
+      </c>
+      <c r="T175" s="6">
+        <v>0.42045448145749448</v>
+      </c>
+      <c r="U175" s="6">
+        <v>0.055672570607946392</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.025074620561484528</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.018895193309492301</v>
+      </c>
+      <c r="X175" s="8">
+        <v>29.5641</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>6.5529923076923078</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>4.532053846153846</v>
+      </c>
+      <c r="AC175" s="8">
+        <v>11.015383999999999</v>
+      </c>
+      <c r="AD175" s="8">
+        <v>17.971792307692308</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.53846153846153844</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-348.69999999999999</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -22335,7 +23392,7 @@
         <v>19898</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C176" s="4">
         <v>44</v>
@@ -22369,25 +23426,57 @@
       <c t="s" r="N176" s="4">
         <v>52</v>
       </c>
-      <c r="O176" s="5"/>
-      <c r="P176" s="5"/>
+      <c r="O176" s="5">
+        <v>1617.2</v>
+      </c>
+      <c r="P176" s="5">
+        <v>1617.2</v>
+      </c>
       <c r="Q176" s="6"/>
-      <c r="R176" s="7"/>
+      <c r="R176" s="7">
+        <v>19</v>
+      </c>
       <c r="S176" s="6"/>
-      <c r="T176" s="6"/>
-      <c r="U176" s="6"/>
-      <c r="V176" s="6"/>
-      <c r="W176" s="6"/>
-      <c r="X176" s="8"/>
-      <c r="Y176" s="6"/>
-      <c r="Z176" s="6"/>
-      <c r="AA176" s="8"/>
-      <c r="AB176" s="8"/>
-      <c r="AC176" s="8"/>
-      <c r="AD176" s="8"/>
-      <c r="AE176" s="6"/>
+      <c r="T176" s="6">
+        <v>-0.014642592134553548</v>
+      </c>
+      <c r="U176" s="6">
+        <v>-0.34740291862478362</v>
+      </c>
+      <c r="V176" s="6">
+        <v>0.016993259955478606</v>
+      </c>
+      <c r="W176" s="6">
+        <v>-0.04828005194162751</v>
+      </c>
+      <c r="X176" s="8">
+        <v>52.802087499999999</v>
+      </c>
+      <c r="Y176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z176" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="AA176" s="8">
+        <v>2.9714285714285715</v>
+      </c>
+      <c r="AB176" s="8">
+        <v>25.670837500000001</v>
+      </c>
+      <c r="AC176" s="8">
+        <v>28.384166</v>
+      </c>
+      <c r="AD176" s="8">
+        <v>35.252087500000002</v>
+      </c>
+      <c r="AE176" s="6">
+        <v>0.125</v>
+      </c>
       <c r="AF176" s="9"/>
-      <c r="AG176" s="5"/>
+      <c r="AG176" s="5">
+        <v>0</v>
+      </c>
       <c r="AH176" s="10">
         <v>3</v>
       </c>
@@ -22506,7 +23595,9 @@
       <c r="AB177" s="8">
         <v>1.6871769230769229</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>5.0333319999999997</v>
+      </c>
       <c r="AD177" s="8">
         <v>11.984615384615385</v>
       </c>
@@ -22635,7 +23726,9 @@
       <c r="AB178" s="8">
         <v>6.2468238095238098</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>9.6134909999999998</v>
+      </c>
       <c r="AD178" s="8">
         <v>16.574604761904762</v>
       </c>
@@ -22762,7 +23855,9 @@
       <c r="AB179" s="8">
         <v>2.0588235294117645</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.5941169999999998</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.534311764705883</v>
       </c>
@@ -22889,7 +23984,9 @@
       <c r="AB180" s="8">
         <v>8.3928571428571423</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>14.555357000000001</v>
+      </c>
       <c r="AD180" s="8">
         <v>20.731249999999999</v>
       </c>
@@ -22940,7 +24037,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -22976,25 +24073,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>2753.3000000000002</v>
+      </c>
+      <c r="P181" s="5">
+        <v>2753.3000000000002</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.49392295170916989</v>
+      </c>
+      <c r="R181" s="7">
+        <v>30</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.11111111111111116</v>
+      </c>
+      <c r="T181" s="6">
+        <v>0.62755166527439799</v>
+      </c>
+      <c r="U181" s="6">
+        <v>0.34392837685686267</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.12536574292666983</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.085893110086078514</v>
+      </c>
+      <c r="X181" s="8">
+        <v>15.68157894736842</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>2.9977766666666668</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>0.43472500000000003</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>3.4092829999999998</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>10.529826315789473</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23113,7 +24246,9 @@
       <c r="AB182" s="8">
         <v>4.5672851851851854</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>9.6256160000000008</v>
+      </c>
       <c r="AD182" s="8">
         <v>15.672857142857142</v>
       </c>
@@ -23242,7 +24377,9 @@
       <c r="AB183" s="8">
         <v>3.4493814814814816</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>8.8366039999999995</v>
+      </c>
       <c r="AD183" s="8">
         <v>16.179886206896551</v>
       </c>
@@ -23371,7 +24508,9 @@
       <c r="AB184" s="8">
         <v>6.0434210526315795</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>13.690089</v>
+      </c>
       <c r="AD184" s="8">
         <v>21.372093023255815</v>
       </c>
@@ -23593,7 +24732,9 @@
       <c r="AB186" s="8">
         <v>6.8058823529411763</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>14.862022</v>
+      </c>
       <c r="AD186" s="8">
         <v>21.312961111111111</v>
       </c>
@@ -23644,7 +24785,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23680,25 +24821,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>1608.4000000000001</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1608.4000000000001</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>0.018458128858635403</v>
+      </c>
+      <c r="R187" s="7">
+        <v>19</v>
+      </c>
+      <c r="S187" s="6">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.32310370554588408</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.13232435961203681</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.077263429495150457</v>
+      </c>
+      <c r="X187" s="8">
+        <v>40.26905</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>8.8964894736842108</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>11.613092857142858</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>21.035713999999999</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>27.973807142857144</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.21428571428571427</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-121.8</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23819,7 +24996,9 @@
       <c r="AB188" s="8">
         <v>5.6791687499999997</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>10.660416</v>
+      </c>
       <c r="AD188" s="8">
         <v>17.616668749999999</v>
       </c>
@@ -23870,7 +25049,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23906,25 +25085,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>3580.2600000000002</v>
+      </c>
+      <c r="P189" s="5">
+        <v>3580.2600000000002</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.16059075614452523</v>
+      </c>
+      <c r="R189" s="7">
+        <v>51</v>
+      </c>
+      <c r="S189" s="6">
+        <v>-0.05555555555555558</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.30804204163943399</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.0010028880584091657</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.06248470781451626</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.022610508734002555</v>
+      </c>
+      <c r="X189" s="8">
+        <v>28.489493478260869</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.065217391304347824</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>4.0235849056603774</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>14.204925000000001</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>18.048401999999999</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>24.155797826086957</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.56521739130434778</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -23965,7 +25180,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24001,25 +25216,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>2592.8200000000002</v>
+      </c>
+      <c r="P190" s="5">
+        <v>2592.8200000000002</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>0.28498647027921775</v>
+      </c>
+      <c r="R190" s="7">
+        <v>32</v>
+      </c>
+      <c r="S190" s="6">
+        <v>0.23076923076923084</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.091536165256361796</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.39096551245362193</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.08029115017625596</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.024953718345276571</v>
+      </c>
+      <c r="X190" s="8">
+        <v>23.34166875</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>3.21875</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>6.06145625</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>9.7572910000000004</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>16.71666875</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.8125</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>0</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24134,7 +25385,9 @@
       <c r="AB191" s="8">
         <v>3.4247137931034484</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>7.0613900000000003</v>
+      </c>
       <c r="AD191" s="8">
         <v>13.877586206896551</v>
       </c>
@@ -24261,7 +25514,9 @@
       <c r="AB192" s="8">
         <v>7.6282076923076927</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>11.180554000000001</v>
+      </c>
       <c r="AD192" s="8">
         <v>17.508976923076922</v>
       </c>
@@ -24388,7 +25643,9 @@
       <c r="AB193" s="8">
         <v>6.0401941176470588</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>12.469042</v>
+      </c>
       <c r="AD193" s="8">
         <v>17.408728571428572</v>
       </c>
@@ -24519,7 +25776,9 @@
       <c r="AB194" s="8">
         <v>4.1685166666666662</v>
       </c>
-      <c r="AC194" s="8"/>
+      <c r="AC194" s="8">
+        <v>9.5229029999999995</v>
+      </c>
       <c r="AD194" s="8">
         <v>16.014910526315788</v>
       </c>
@@ -24648,7 +25907,9 @@
       <c r="AB195" s="8">
         <v>6.1838899999999999</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>9.9249989999999997</v>
+      </c>
       <c r="AD195" s="8">
         <v>16.854443333333332</v>
       </c>
@@ -24777,7 +26038,9 @@
       <c r="AB196" s="8">
         <v>13.334615384615384</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>22.733927999999999</v>
+      </c>
       <c r="AD196" s="8">
         <v>27.461907142857143</v>
       </c>
@@ -24906,7 +26169,9 @@
       <c r="AB197" s="8">
         <v>6.9483666666666659</v>
       </c>
-      <c r="AC197" s="8"/>
+      <c r="AC197" s="8">
+        <v>9.0986799999999999</v>
+      </c>
       <c r="AD197" s="8">
         <v>15.827563461538462</v>
       </c>
@@ -25035,7 +26300,9 @@
       <c r="AB198" s="8">
         <v>4.3166666666666664</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>15.224999</v>
+      </c>
       <c r="AD198" s="8">
         <v>20.75714285714286</v>
       </c>
@@ -25086,7 +26353,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -25122,25 +26389,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>2413.6999999999998</v>
+      </c>
+      <c r="P199" s="5">
+        <v>2413.6999999999998</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.38791553503186327</v>
+      </c>
+      <c r="R199" s="7">
+        <v>28</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.41666666666666663</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.35093698471226747</v>
+      </c>
+      <c r="U199" s="6">
+        <v>-0.044729419563326017</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.053248539586526915</v>
+      </c>
+      <c r="W199" s="6">
+        <v>0.0087028213945395047</v>
+      </c>
+      <c r="X199" s="8">
+        <v>22.482219999999998</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>4.3752862068965523</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>5.5730769230769237</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>10.258492</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>15.564446666666667</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.8666666666666667</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>0</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -25181,7 +26484,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25217,25 +26520,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>1531.5899999999999</v>
+      </c>
+      <c r="P200" s="5">
+        <v>1531.5899999999999</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.85989945110992361</v>
+      </c>
+      <c r="R200" s="7">
+        <v>21</v>
+      </c>
+      <c r="S200" s="6">
+        <v>0.23529411764705888</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.38520100026769571</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.1303684406401191</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.06396032880862372</v>
+      </c>
+      <c r="X200" s="8">
+        <v>29.15909090909091</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>7.0848500000000003</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>8.0515181818181816</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>16.79457</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>23.727272727272727</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.54545454545454541</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-156.19999999999999</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25447,7 +26786,9 @@
       <c r="AB202" s="8">
         <v>5.0250000000000004</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>11.652777</v>
+      </c>
       <c r="AD202" s="8">
         <v>16.507411111111111</v>
       </c>
@@ -25669,7 +27010,9 @@
       <c r="AB204" s="8">
         <v>1.6931352941176472</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>9.6558820000000001</v>
+      </c>
       <c r="AD204" s="8">
         <v>16.594117647058823</v>
       </c>
@@ -25794,7 +27137,9 @@
       <c r="AB205" s="8">
         <v>1.7399999999999998</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>6.5199999999999996</v>
+      </c>
       <c r="AD205" s="8">
         <v>13.473339999999999</v>
       </c>
@@ -25919,7 +27264,9 @@
       <c r="AB206" s="8">
         <v>3.7309571428571431</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>15.564285</v>
+      </c>
       <c r="AD206" s="8">
         <v>21.699999999999999</v>
       </c>
@@ -26044,7 +27391,9 @@
       <c r="AB207" s="8">
         <v>13.899999999999999</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>19.118518000000002</v>
+      </c>
       <c r="AD207" s="8">
         <v>26.085188888888887</v>
       </c>
@@ -26169,7 +27518,9 @@
       <c r="AB208" s="8">
         <v>5.7350000000000003</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>20.546665999999998</v>
+      </c>
       <c r="AD208" s="8">
         <v>27.496665</v>
       </c>
@@ -26478,7 +27829,9 @@
       <c r="AB211" s="8">
         <v>2.836665</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>8.6058319999999995</v>
+      </c>
       <c r="AD211" s="8">
         <v>15.551665</v>
       </c>
@@ -26953,22 +28306,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -26978,10 +28333,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
@@ -912,30 +912,30 @@
   </si>
   <si>
     <t>214
-166</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 726.068,14</t>
-  </si>
-  <si>
-    <t>R$ 4.033,71
-R$ 4.186,35</t>
+167</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 727.960,88</t>
+  </si>
+  <si>
+    <t>R$ 4.021,88
+R$ 4.172,62</t>
   </si>
   <si>
     <t>(7.4%)
-(3.9%)</t>
-  </si>
-  <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>(13.3%)</t>
-  </si>
-  <si>
-    <t>43.3%</t>
+(4.1%)</t>
+  </si>
+  <si>
+    <t>45.0</t>
+  </si>
+  <si>
+    <t>(13.4%)</t>
+  </si>
+  <si>
+    <t>43.2%</t>
   </si>
   <si>
     <t>(3.5%)</t>
@@ -950,7 +950,7 @@
     <t>26.2</t>
   </si>
   <si>
-    <t>74.1%</t>
+    <t>74.0%</t>
   </si>
   <si>
     <t>8.4%</t>
@@ -962,7 +962,7 @@
     <t>6.8</t>
   </si>
   <si>
-    <t>11.4</t>
+    <t>11.5</t>
   </si>
   <si>
     <t>18.1</t>
@@ -6002,7 +6002,9 @@
       <c r="AB36" s="8">
         <v>6.1235620689655175</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>14.416895999999999</v>
+      </c>
       <c r="AD36" s="8">
         <v>20.723889999999997</v>
       </c>
@@ -14172,7 +14174,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14208,25 +14210,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>1892.74</v>
+      </c>
+      <c r="P102" s="5">
+        <v>1892.74</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.3120411160058737</v>
+      </c>
+      <c r="R102" s="7">
+        <v>22</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.37142857142857144</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.0028765704745501233</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.32250356625844012</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.024223612329215844</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.016975918509673806</v>
+      </c>
+      <c r="X102" s="8">
+        <v>30.95462777777778</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>5.5106045454545454</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>7.0601833333333328</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>12.452776999999999</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>19.387038888888888</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -20725,7 +20763,7 @@
         <v>0.018193099782291763</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.026704827494557295</v>
+        <v>-0.021561128330603838</v>
       </c>
       <c r="X154" s="8">
         <v>27.007692307692309</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
@@ -911,37 +911,40 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-167</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 727.960,88</t>
-  </si>
-  <si>
-    <t>R$ 4.021,88
-R$ 4.172,62</t>
-  </si>
-  <si>
-    <t>(7.4%)
-(4.1%)</t>
-  </si>
-  <si>
-    <t>45.0</t>
-  </si>
-  <si>
-    <t>(13.4%)</t>
-  </si>
-  <si>
-    <t>43.2%</t>
-  </si>
-  <si>
-    <t>(3.5%)</t>
-  </si>
-  <si>
-    <t>3.9%</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+170</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 742.545,32</t>
+  </si>
+  <si>
+    <t>R$ 4.035,57
+R$ 4.184,77</t>
+  </si>
+  <si>
+    <t>(7.6%)
+(4.3%)</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>(13.7%)</t>
+  </si>
+  <si>
+    <t>42.8%</t>
+  </si>
+  <si>
+    <t>(3.6%)</t>
+  </si>
+  <si>
+    <t>4.0%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -950,7 +953,7 @@
     <t>26.2</t>
   </si>
   <si>
-    <t>74.0%</t>
+    <t>73.9%</t>
   </si>
   <si>
     <t>8.4%</t>
@@ -959,19 +962,19 @@
     <t>4.6</t>
   </si>
   <si>
-    <t>6.8</t>
+    <t>6.7</t>
   </si>
   <si>
     <t>11.5</t>
   </si>
   <si>
-    <t>18.1</t>
-  </si>
-  <si>
-    <t>74.4%</t>
-  </si>
-  <si>
-    <t>-R$ 16.749,01</t>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>74.5%</t>
+  </si>
+  <si>
+    <t>-R$ 16.927,41</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2249,10 +2252,10 @@
         <v>-0.13636363636363635</v>
       </c>
       <c r="T7" s="6">
-        <v>0.51716789617413994</v>
+        <v>0.51763212571515316</v>
       </c>
       <c r="U7" s="6">
-        <v>0.038189561278546551</v>
+        <v>0.038653790819559851</v>
       </c>
       <c r="V7" s="6">
         <v>0.030814652410381883</v>
@@ -5694,7 +5697,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5730,25 +5733,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>8711.0900000000001</v>
+      </c>
+      <c r="P34" s="5">
+        <v>8711.0900000000001</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0.25264265900891125</v>
+      </c>
+      <c r="R34" s="7">
+        <v>86</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.033707865168539297</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.24312745018132059</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-0.095480003076538075</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.079591589571454319</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.04847952437639836</v>
+      </c>
+      <c r="X34" s="8">
+        <v>23.537420754716983</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.11320754716981132</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>9.91144578313253</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.2846938775510206</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>11.846393000000001</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>17.119811320754717</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.79245283018867929</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>-98.700000000000003</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -10984,7 +11023,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -11018,25 +11057,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>4251.7700000000004</v>
+      </c>
+      <c r="P76" s="5">
+        <v>4251.7700000000004</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.43411140569432904</v>
+      </c>
+      <c r="R76" s="7">
+        <v>53</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.4854368932038835</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.27511768040133872</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.089866784891939111</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.078328084538909673</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.032295491054313848</v>
+      </c>
+      <c r="X76" s="8">
+        <v>25.419642857142858</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.72413793103448276</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>2.6326803921568627</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>5.4716037037037042</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>8.1960479999999993</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>16.643679310344826</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.6785714285714286</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-79.700000000000003</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -15932,7 +16007,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>23.601216999999998</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19069,7 +19146,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19105,25 +19182,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>1621.5799999999999</v>
+      </c>
+      <c r="P141" s="5">
+        <v>1621.5799999999999</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>-0.37317402211854023</v>
+      </c>
+      <c r="R141" s="7">
+        <v>26</v>
+      </c>
+      <c r="S141" s="6">
+        <v>-0.1875</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.30670611379025398</v>
+      </c>
+      <c r="U141" s="6">
+        <v>-0.03759388990984102</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.17075537438794264</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.055324745001788377</v>
+      </c>
+      <c r="X141" s="8">
+        <v>20.040275000000001</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>3.7007260869565215</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>2.1555583333333335</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>5.6333320000000002</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>13.573608333333333</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28281,112 +28394,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
@@ -915,27 +915,27 @@
   </si>
   <si>
     <t>215
-170</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 742.545,32</t>
-  </si>
-  <si>
-    <t>R$ 4.035,57
-R$ 4.184,77</t>
-  </si>
-  <si>
-    <t>(7.6%)
-(4.3%)</t>
+171</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 746.400,68</t>
+  </si>
+  <si>
+    <t>R$ 4.034,60
+R$ 4.182,85</t>
+  </si>
+  <si>
+    <t>(7.9%)
+(4.6%)</t>
   </si>
   <si>
     <t>45.2</t>
   </si>
   <si>
-    <t>(13.7%)</t>
+    <t>(13.8%)</t>
   </si>
   <si>
     <t>42.8%</t>
@@ -953,7 +953,7 @@
     <t>26.2</t>
   </si>
   <si>
-    <t>73.9%</t>
+    <t>73.8%</t>
   </si>
   <si>
     <t>8.4%</t>
@@ -11113,7 +11113,7 @@
         <v>-79.700000000000003</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16537,7 +16537,7 @@
         <v>-41.899999999999999</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -21396,7 +21396,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21432,27 +21432,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>3855.3600000000001</v>
+      </c>
+      <c r="P159" s="5">
+        <v>3855.3600000000001</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>-0.37366215030704741</v>
+      </c>
+      <c r="R159" s="7">
+        <v>49</v>
+      </c>
+      <c r="S159" s="6">
+        <v>-0.19672131147540983</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.27858264857237713</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.017034362549800796</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.078658542911686585</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.022119075780212483</v>
+      </c>
+      <c r="X159" s="8">
+        <v>25.323437500000001</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>3.8710877551020411</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>4.4040241379310343</v>
+      </c>
       <c r="AC159" s="8">
         <v>8.5398800000000001</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>14.609896875</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.78125</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>0</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
@@ -915,30 +915,30 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 746.400,68</t>
-  </si>
-  <si>
-    <t>R$ 4.034,60
-R$ 4.182,85</t>
+172</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 749.687,20</t>
+  </si>
+  <si>
+    <t>R$ 4.030,58
+R$ 4.177,63</t>
   </si>
   <si>
     <t>(7.9%)
 (4.6%)</t>
   </si>
   <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>(13.8%)</t>
-  </si>
-  <si>
-    <t>42.8%</t>
+    <t>45.1</t>
+  </si>
+  <si>
+    <t>(13.9%)</t>
+  </si>
+  <si>
+    <t>42.7%</t>
   </si>
   <si>
     <t>(3.6%)</t>
@@ -4876,7 +4876,7 @@
         <v>-156.94999999999999</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12676,7 +12676,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12710,25 +12710,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>3286.52</v>
+      </c>
+      <c r="P89" s="5">
+        <v>3286.52</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.15048905064207274</v>
+      </c>
+      <c r="R89" s="7">
+        <v>27</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.3571428571428571</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.30858780716380851</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.036800019473485636</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0064305100836142791</v>
+      </c>
+      <c r="X89" s="8">
+        <v>27.855553333333333</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.2858037037037038</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>5.4955533333333335</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>19.796666666666667</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14210,7 +14244,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -20115,10 +20149,10 @@
         <v>0.083333333333333259</v>
       </c>
       <c r="T148" s="6">
-        <v>-4.0971450415028405</v>
+        <v>-3.8752814703863194</v>
       </c>
       <c r="U148" s="6">
-        <v>-4.3791729597037596</v>
+        <v>-4.1573093885872394</v>
       </c>
       <c r="V148" s="6">
         <v>0.030036510016850777</v>
@@ -24746,7 +24780,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25713,7 +25747,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27024,7 +27058,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28433,7 +28467,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-07).xlsx
@@ -915,48 +915,48 @@
   </si>
   <si>
     <t>215
-172</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 749.687,20</t>
-  </si>
-  <si>
-    <t>R$ 4.030,58
-R$ 4.177,63</t>
-  </si>
-  <si>
-    <t>(7.9%)
-(4.6%)</t>
-  </si>
-  <si>
-    <t>45.1</t>
-  </si>
-  <si>
-    <t>(13.9%)</t>
-  </si>
-  <si>
-    <t>42.7%</t>
+177</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 759.944,86</t>
+  </si>
+  <si>
+    <t>R$ 3.978,77
+R$ 4.117,57</t>
+  </si>
+  <si>
+    <t>(8.1%)
+(4.9%)</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>(14.0%)</t>
+  </si>
+  <si>
+    <t>42.4%</t>
   </si>
   <si>
     <t>(3.6%)</t>
   </si>
   <si>
-    <t>4.0%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>26.2</t>
-  </si>
-  <si>
-    <t>73.8%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
+    <t>4.1%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>26.1</t>
+  </si>
+  <si>
+    <t>73.9%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
   </si>
   <si>
     <t>4.6</t>
@@ -965,16 +965,16 @@
     <t>6.7</t>
   </si>
   <si>
-    <t>11.5</t>
+    <t>11.4</t>
   </si>
   <si>
     <t>18.0</t>
   </si>
   <si>
-    <t>74.5%</t>
-  </si>
-  <si>
-    <t>-R$ 16.927,41</t>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>-R$ 16.968,31</t>
   </si>
   <si>
     <t>2.94</t>
@@ -7922,7 +7922,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7958,25 +7958,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>498.10000000000002</v>
+      </c>
+      <c r="P51" s="5">
+        <v>498.10000000000002</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.32975402335970716</v>
+      </c>
+      <c r="R51" s="7">
+        <v>7</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.22222222222222221</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.31427424212005617</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.088500301144348523</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.1684962858863682</v>
+      </c>
+      <c r="X51" s="8">
+        <v>23.772233333333332</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>1.4785714285714284</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>11.75</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>20.794433333333334</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8849,7 +8883,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>8.8906489999999998</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20490,7 +20526,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20526,25 +20562,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2740.8400000000001</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2740.8400000000001</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.30115198090740802</v>
+      </c>
+      <c r="R151" s="7">
+        <v>32</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.27272727272727271</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.18475879657331329</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.11981936194743217</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.08805457451000423</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.040631156871615996</v>
+      </c>
+      <c r="X151" s="8">
+        <v>22.645556666666668</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>4.0125000000000002</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.3144433333333336</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>6.5214740000000004</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>13.386666666666667</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21240,7 +21312,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21276,25 +21348,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>1924.5999999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>1924.5999999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.24571930223352689</v>
+      </c>
+      <c r="R157" s="7">
+        <v>20</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.2592592592592593</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.22379226852332954</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.10515920191208564</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.090434116179985452</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.044003689078250023</v>
+      </c>
+      <c r="X157" s="8">
+        <v>25.116666666666667</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>5.8008350000000002</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.8133333333333335</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>9.6266660000000002</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>16.568886666666668</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21335,7 +21443,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21371,25 +21479,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2117.8400000000001</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2117.8400000000001</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.20090254274060571</v>
+      </c>
+      <c r="R158" s="7">
+        <v>22</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.3125</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.28583051599743131</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.0045816964454349716</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.065438607260227405</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.010561940467646282</v>
+      </c>
+      <c r="X158" s="8">
+        <v>24.563888888888886</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>4.4127000000000001</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>3.8620388888888888</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>8.1101849999999995</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>15.058333333333334</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.77777777777777779</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22206,7 +22350,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22242,25 +22386,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>2976.2800000000002</v>
+      </c>
+      <c r="P165" s="5">
+        <v>2976.2800000000002</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.14581240636677251</v>
+      </c>
+      <c r="R165" s="7">
+        <v>31</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.31111111111111112</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.28830039512411465</v>
+      </c>
+      <c r="U165" s="6">
+        <v>0.01486510005779026</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.10183416882820163</v>
+      </c>
+      <c r="W165" s="6">
+        <v>0.054271439515099378</v>
+      </c>
+      <c r="X165" s="8">
+        <v>20.689130434782609</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>4.402776666666667</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>2.2287863636363636</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>6.7022709999999996</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>13.254347826086958</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-40.899999999999999</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
